--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CDP.xlsx
@@ -13,9 +13,9 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$A$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,11 @@
           <t>team_name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,36 +472,96 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>primary_scorer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker (23.3 net)</t>
+          <t>A. Bah (13.5 ppg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>most_used_player</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B. Whitaker (25.6 mpg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>best_3pt_pct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B. Gomes (36.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>base_lineup</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (21.5 min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (18.6 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker (16.5 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>B. Gomes | J. Costa | M. Rodrigues (16.3 net)</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker | J. Rodrigues (12.2 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -508,28 +572,544 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>playing_position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games_started</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes_total</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bpg</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tp_pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ft_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>efg_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ts_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>plus_minus_pg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>on_off_net_diff_per40</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>role_tag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B. Whitaker</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>38.3%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>high-minutes, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B. Gomes</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>54.8%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>high-minutes, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M. Lamut</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>50.7%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>16</v>
+      </c>
+      <c r="T4" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>high-minutes, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>42.3%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>51.9%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>51.9%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>primary-scorer, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>23.0%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:U6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -540,28 +1120,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lineup_players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>team_rank_minutes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>team_rank_net</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>team_rank_defense</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>Base lineup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Best lineup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rotation lineup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B. Gomes | D. Buccilli | J. Costa | J. Pedro | M. Rodrigues</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G5" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:L5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -661,22 +1476,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>22.3</v>
+        <v>46.2</v>
       </c>
       <c r="H2" t="n">
-        <v>80.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>57.4</v>
+        <v>55.4</v>
       </c>
       <c r="J2" t="n">
-        <v>23.3</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="3">
@@ -697,26 +1512,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Whitaker | J. Rodrigues</t>
+          <t>A. Bah | M. Lamut</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>17.1</v>
+        <v>38.9</v>
       </c>
       <c r="H3" t="n">
-        <v>72.5</v>
+        <v>78.2</v>
       </c>
       <c r="I3" t="n">
-        <v>49.1</v>
+        <v>52.5</v>
       </c>
       <c r="J3" t="n">
-        <v>23.4</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="4">
@@ -737,26 +1552,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Whitaker | J. Rodrigues</t>
+          <t>A. Bah | M. Lamut</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>17.1</v>
+        <v>38.9</v>
       </c>
       <c r="H4" t="n">
-        <v>72.5</v>
+        <v>78.2</v>
       </c>
       <c r="I4" t="n">
-        <v>49.1</v>
+        <v>52.5</v>
       </c>
       <c r="J4" t="n">
-        <v>23.4</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="5">
@@ -777,26 +1592,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Gomes | J. Costa | M. Rodrigues</t>
+          <t>A. Bah | B. Whitaker | J. Rodrigues</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>17.2</v>
+        <v>39.4</v>
       </c>
       <c r="H5" t="n">
-        <v>90.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I5" t="n">
-        <v>74.3</v>
+        <v>53.9</v>
       </c>
       <c r="J5" t="n">
-        <v>16.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="6">
@@ -821,22 +1636,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>16.8</v>
+        <v>38.7</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>78.5</v>
       </c>
       <c r="I6" t="n">
-        <v>52.2</v>
+        <v>52.7</v>
       </c>
       <c r="J6" t="n">
-        <v>42.7</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="7">
@@ -857,26 +1672,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | J. Rodrigues</t>
+          <t>A. Bah | J. Rodrigues | M. Lamut</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>16.8</v>
+        <v>32.7</v>
       </c>
       <c r="H7" t="n">
-        <v>74</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>50.1</v>
+        <v>48.9</v>
       </c>
       <c r="J7" t="n">
-        <v>23.9</v>
+        <v>24.5</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CDP.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Bah (13.5 ppg)</t>
+          <t>A. Bah (13 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B. Whitaker (25.6 mpg)</t>
+          <t>B. Whitaker (26.8 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B. Gomes (36.4%)</t>
+          <t>M. Rodrigues (42.9%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (21.5 min)</t>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (26.4 min)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (18.6 net)</t>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (27.3 net)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker (16.5 net)</t>
+          <t>A. Bah | B. Whitaker (10.1 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | J. Rodrigues (12.2 net)</t>
+          <t>A. Bah | B. Whitaker | M. Lamut (14.0 net)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="38" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -718,69 +718,69 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>51.2</v>
+        <v>80.5</v>
       </c>
       <c r="G2" t="n">
-        <v>25.6</v>
+        <v>26.8</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>12.7</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
-        <v>1.5</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>16.6</v>
+        <v>22.2</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>high-minutes, impact</t>
+          <t>high-minutes, primary-scorer, impact</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>M. Lamut</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -801,48 +801,48 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>48.3</v>
+        <v>73.3</v>
       </c>
       <c r="G3" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="H3" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -852,18 +852,18 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>10.3</v>
       </c>
       <c r="T3" t="n">
-        <v>-15.7</v>
+        <v>27.9</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>high-minutes, shooter</t>
+          <t>high-minutes, impact</t>
         </is>
       </c>
     </row>
@@ -875,78 +875,74 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M. Lamut</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>A. Bah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>48.3</v>
+        <v>70.3</v>
       </c>
       <c r="G4" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="H4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>41.0%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>47.8%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T4" t="n">
         <v>8.5</v>
       </c>
-      <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>46.7%</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>46.7%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>50.7%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>16</v>
-      </c>
-      <c r="T4" t="n">
-        <v>34.5</v>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, impact</t>
+          <t>primary-scorer, impact</t>
         </is>
       </c>
     </row>
@@ -958,70 +954,78 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Bah</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>J. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>35.7%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="T5" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>primary-scorer, impact</t>
+          <t>impact</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1037,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Rodrigues</t>
+          <t>D. Buccilli</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1042,38 +1046,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>52.9</v>
       </c>
       <c r="G6" t="n">
-        <v>21.5</v>
+        <v>17.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1088,28 +1092,356 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="S6" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Okemirie</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>49</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>53.0%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B. Gomes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>54.8%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>high-minutes, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M. Rodrigues</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>57.3%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Costa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H10" t="n">
         <v>5</v>
       </c>
-      <c r="T6" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="I10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>50.8%</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U6"/>
+  <autoFilter ref="A1:U10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1216,31 +1548,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>21.5</v>
+        <v>26.4</v>
       </c>
       <c r="G2" t="n">
-        <v>74.2</v>
+        <v>75.7</v>
       </c>
       <c r="H2" t="n">
-        <v>55.7</v>
+        <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>18.6</v>
+        <v>27.3</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1260,31 +1592,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>21.5</v>
+        <v>26.4</v>
       </c>
       <c r="G3" t="n">
-        <v>74.2</v>
+        <v>75.7</v>
       </c>
       <c r="H3" t="n">
-        <v>55.7</v>
+        <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>18.6</v>
+        <v>27.3</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1304,31 +1636,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>21.5</v>
+        <v>26.4</v>
       </c>
       <c r="G4" t="n">
-        <v>74.2</v>
+        <v>75.7</v>
       </c>
       <c r="H4" t="n">
-        <v>55.7</v>
+        <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>18.6</v>
+        <v>27.3</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -1369,10 +1701,10 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L5" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1393,7 +1725,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1476,22 +1808,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>46.2</v>
+        <v>63.2</v>
       </c>
       <c r="H2" t="n">
-        <v>71.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="I2" t="n">
-        <v>55.4</v>
+        <v>57.6</v>
       </c>
       <c r="J2" t="n">
-        <v>16.5</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="3">
@@ -1512,26 +1844,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A. Bah | M. Lamut</t>
+          <t>J. Rodrigues | M. Lamut</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>38.9</v>
+        <v>48.8</v>
       </c>
       <c r="H3" t="n">
-        <v>78.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>52.5</v>
+        <v>56.6</v>
       </c>
       <c r="J3" t="n">
-        <v>25.7</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="4">
@@ -1552,26 +1884,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A. Bah | M. Lamut</t>
+          <t>J. Rodrigues | M. Lamut</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>38.9</v>
+        <v>48.8</v>
       </c>
       <c r="H4" t="n">
-        <v>78.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>52.5</v>
+        <v>56.6</v>
       </c>
       <c r="J4" t="n">
-        <v>25.7</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="5">
@@ -1592,26 +1924,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | J. Rodrigues</t>
+          <t>A. Bah | B. Whitaker | M. Lamut</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>39.4</v>
+        <v>54.2</v>
       </c>
       <c r="H5" t="n">
-        <v>66</v>
+        <v>70.8</v>
       </c>
       <c r="I5" t="n">
-        <v>53.9</v>
+        <v>56.8</v>
       </c>
       <c r="J5" t="n">
-        <v>12.2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -1632,26 +1964,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | M. Lamut</t>
+          <t>B. Whitaker | J. Rodrigues | M. Lamut</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>38.7</v>
+        <v>40.3</v>
       </c>
       <c r="H6" t="n">
-        <v>78.5</v>
+        <v>75.3</v>
       </c>
       <c r="I6" t="n">
-        <v>52.7</v>
+        <v>51.5</v>
       </c>
       <c r="J6" t="n">
-        <v>25.8</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="7">
@@ -1672,26 +2004,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A. Bah | J. Rodrigues | M. Lamut</t>
+          <t>B. Whitaker | J. Rodrigues | M. Lamut</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>32.7</v>
+        <v>40.3</v>
       </c>
       <c r="H7" t="n">
-        <v>73.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="I7" t="n">
-        <v>48.9</v>
+        <v>51.5</v>
       </c>
       <c r="J7" t="n">
-        <v>24.5</v>
+        <v>23.8</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CDP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CDP.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Bah (13 ppg)</t>
+          <t>B. Whitaker (13.5 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B. Whitaker (26.8 mpg)</t>
+          <t>B. Whitaker (27.4 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Rodrigues (42.9%)</t>
+          <t>M. Rodrigues (42.1%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (26.4 min)</t>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (36.2 min)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (27.3 net)</t>
+          <t>A. Bah | B. Whitaker | J. Okemirie | J. Rodrigues | M. Lamut (9.9 net)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker (10.1 net)</t>
+          <t>A. Bah | M. Lamut (10.2 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker | M. Lamut (14.0 net)</t>
+          <t>A. Bah | B. Whitaker | M. Lamut (8.0 net)</t>
         </is>
       </c>
     </row>
@@ -572,11 +572,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -718,65 +718,65 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>80.5</v>
+        <v>109.7</v>
       </c>
       <c r="G2" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="H2" t="n">
-        <v>12.7</v>
+        <v>13.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>8.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>22.2</v>
+        <v>8.9</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -801,65 +801,65 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>73.3</v>
+        <v>101.7</v>
       </c>
       <c r="G3" t="n">
-        <v>24.4</v>
+        <v>25.4</v>
       </c>
       <c r="H3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>48.4%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>63.2%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>48.4%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>53.4%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>70.0%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>55.3%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>10.3</v>
-      </c>
       <c r="T3" t="n">
-        <v>27.9</v>
+        <v>30.6</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -880,69 +880,69 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>70.3</v>
+        <v>96.2</v>
       </c>
       <c r="G4" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>8.5</v>
+        <v>14</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>primary-scorer, impact</t>
+          <t>high-minutes, impact</t>
         </is>
       </c>
     </row>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>67.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="G5" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1009,19 +1009,19 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="T5" t="n">
-        <v>15</v>
+        <v>17.9</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1046,65 +1046,65 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>52.9</v>
+        <v>69.8</v>
       </c>
       <c r="G6" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>-1.3</v>
+        <v>-4.5</v>
       </c>
       <c r="T6" t="n">
-        <v>-17.1</v>
+        <v>-21</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1120,74 +1120,78 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Okemirie</t>
+          <t>Betinho Gomes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>68.3</v>
       </c>
       <c r="G7" t="n">
-        <v>16.3</v>
+        <v>22.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>10.7</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.7</v>
       </c>
-      <c r="K7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>4.7</v>
+        <v>-3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>5.3</v>
+        <v>-19.8</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>efficient, shooter</t>
         </is>
       </c>
     </row>
@@ -1199,31 +1203,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B. Gomes</t>
+          <t>J. Okemirie</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>48.3</v>
+        <v>66.8</v>
       </c>
       <c r="G8" t="n">
-        <v>24.2</v>
+        <v>16.7</v>
       </c>
       <c r="H8" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
         <v>0.5</v>
@@ -1232,45 +1236,41 @@
         <v>1.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>-15.7</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>high-minutes, shooter</t>
+          <t>rotation</t>
         </is>
       </c>
     </row>
@@ -1291,28 +1291,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>42.7</v>
+        <v>52.2</v>
       </c>
       <c r="G9" t="n">
-        <v>14.2</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1337,19 +1337,19 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>-1.7</v>
+        <v>-0.8</v>
       </c>
       <c r="T9" t="n">
-        <v>-9.199999999999999</v>
+        <v>-1.1</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1365,83 +1365,162 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Costa</t>
+          <t>J. Pedro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>40.4</v>
+        <v>50.9</v>
       </c>
       <c r="G10" t="n">
-        <v>13.5</v>
+        <v>12.7</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>62.9%</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Costa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="F11" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>50.8%</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-19.5</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U10"/>
+  <autoFilter ref="A1:U11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1548,31 +1627,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>26.4</v>
+        <v>36.2</v>
       </c>
       <c r="G2" t="n">
-        <v>75.7</v>
+        <v>68.5</v>
       </c>
       <c r="H2" t="n">
-        <v>48.5</v>
+        <v>58.5</v>
       </c>
       <c r="I2" t="n">
-        <v>27.3</v>
+        <v>9.9</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1592,31 +1671,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>26.4</v>
+        <v>36.2</v>
       </c>
       <c r="G3" t="n">
-        <v>75.7</v>
+        <v>68.5</v>
       </c>
       <c r="H3" t="n">
-        <v>48.5</v>
+        <v>58.5</v>
       </c>
       <c r="I3" t="n">
-        <v>27.3</v>
+        <v>9.9</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -1636,31 +1715,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>26.4</v>
+        <v>36.2</v>
       </c>
       <c r="G4" t="n">
-        <v>75.7</v>
+        <v>68.5</v>
       </c>
       <c r="H4" t="n">
-        <v>48.5</v>
+        <v>58.5</v>
       </c>
       <c r="I4" t="n">
-        <v>27.3</v>
+        <v>9.9</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1676,35 +1755,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B. Gomes | D. Buccilli | J. Costa | J. Pedro | M. Rodrigues</t>
+          <t>Betinho Gomes | D. Buccilli | J. Costa | J. Pedro | M. Rodrigues</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="G5" t="n">
-        <v>94.8</v>
+        <v>98.3</v>
       </c>
       <c r="H5" t="n">
-        <v>94.8</v>
+        <v>96</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1725,7 +1804,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1804,26 +1883,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A. Bah | B. Whitaker</t>
+          <t>A. Bah | M. Lamut</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>63.2</v>
+        <v>82.3</v>
       </c>
       <c r="H2" t="n">
-        <v>67.7</v>
+        <v>73.8</v>
       </c>
       <c r="I2" t="n">
-        <v>57.6</v>
+        <v>63.6</v>
       </c>
       <c r="J2" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="3">
@@ -1848,22 +1927,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>48.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>77.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="I3" t="n">
-        <v>56.6</v>
+        <v>60.6</v>
       </c>
       <c r="J3" t="n">
-        <v>21.3</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="4">
@@ -1884,26 +1963,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>J. Rodrigues | M. Lamut</t>
+          <t>B. Whitaker | J. Rodrigues</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>48.8</v>
+        <v>67</v>
       </c>
       <c r="H4" t="n">
-        <v>77.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="I4" t="n">
-        <v>56.6</v>
+        <v>59.1</v>
       </c>
       <c r="J4" t="n">
-        <v>21.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5">
@@ -1928,22 +2007,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>54.2</v>
+        <v>70</v>
       </c>
       <c r="H5" t="n">
-        <v>70.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>56.8</v>
+        <v>61.1</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1964,26 +2043,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Whitaker | J. Rodrigues | M. Lamut</t>
+          <t>A. Bah | J. Rodrigues | M. Lamut</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>40.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>75.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>51.5</v>
+        <v>60.3</v>
       </c>
       <c r="J6" t="n">
-        <v>23.8</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="7">
@@ -2004,26 +2083,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B. Whitaker | J. Rodrigues | M. Lamut</t>
+          <t>A. Bah | B. Whitaker | J. Rodrigues</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>40.3</v>
+        <v>63.4</v>
       </c>
       <c r="H7" t="n">
-        <v>75.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>51.5</v>
+        <v>57.4</v>
       </c>
       <c r="J7" t="n">
-        <v>23.8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
